--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -2932,6 +2932,63 @@
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled DS (for DSRA)</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Based on straight-line amort</t>
+        </is>
+      </c>
+      <c r="E93" s="18">
+        <f>MAX(0,$D$57-(1-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="F93" s="18">
+        <f>MAX(0,$D$57-(2-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="G93" s="18">
+        <f>MAX(0,$D$57-(3-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="H93" s="18">
+        <f>MAX(0,$D$57-(4-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="I93" s="18">
+        <f>MAX(0,$D$57-(5-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="J93" s="18">
+        <f>MAX(0,$D$57-(6-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="K93" s="18">
+        <f>MAX(0,$D$57-(7-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="L93" s="18">
+        <f>MAX(0,$D$57-(8-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="M93" s="18">
+        <f>MAX(0,$D$57-(9-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+      <c r="N93" s="18">
+        <f>MAX(0,$D$57-(10-1)*$D$59)*$D$43+$D$59</f>
+        <v/>
+      </c>
+    </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
@@ -2965,47 +3022,47 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
         </is>
       </c>
       <c r="D95" s="18">
-        <f>E87*$D$45/12</f>
+        <f>E93*$D$45/12</f>
         <v/>
       </c>
       <c r="E95" s="18">
-        <f>F87*$D$45/12</f>
+        <f>F93*$D$45/12</f>
         <v/>
       </c>
       <c r="F95" s="18">
-        <f>G87*$D$45/12</f>
+        <f>G93*$D$45/12</f>
         <v/>
       </c>
       <c r="G95" s="18">
-        <f>H87*$D$45/12</f>
+        <f>H93*$D$45/12</f>
         <v/>
       </c>
       <c r="H95" s="18">
-        <f>I87*$D$45/12</f>
+        <f>I93*$D$45/12</f>
         <v/>
       </c>
       <c r="I95" s="18">
-        <f>J87*$D$45/12</f>
+        <f>J93*$D$45/12</f>
         <v/>
       </c>
       <c r="J95" s="18">
-        <f>K87*$D$45/12</f>
+        <f>K93*$D$45/12</f>
         <v/>
       </c>
       <c r="K95" s="18">
-        <f>L87*$D$45/12</f>
+        <f>L93*$D$45/12</f>
         <v/>
       </c>
       <c r="L95" s="18">
-        <f>M87*$D$45/12</f>
+        <f>M93*$D$45/12</f>
         <v/>
       </c>
       <c r="M95" s="18">
-        <f>N87*$D$45/12</f>
+        <f>N93*$D$45/12</f>
         <v/>
       </c>
       <c r="N95" s="18">

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -1895,43 +1895,43 @@
         </is>
       </c>
       <c r="E70" s="18">
-        <f>$D$56*$D$24*E64/1000000000</f>
+        <f>$D$56*$D$24*E64/1E9</f>
         <v/>
       </c>
       <c r="F70" s="18">
-        <f>$D$56*$D$24*F64/1000000000</f>
+        <f>$D$56*$D$24*F64/1E9</f>
         <v/>
       </c>
       <c r="G70" s="18">
-        <f>$D$56*$D$24*G64/1000000000</f>
+        <f>$D$56*$D$24*G64/1E9</f>
         <v/>
       </c>
       <c r="H70" s="18">
-        <f>$D$56*$D$24*H64/1000000000</f>
+        <f>$D$56*$D$24*H64/1E9</f>
         <v/>
       </c>
       <c r="I70" s="18">
-        <f>$D$56*$D$24*I64/1000000000</f>
+        <f>$D$56*$D$24*I64/1E9</f>
         <v/>
       </c>
       <c r="J70" s="18">
-        <f>$D$56*$D$24*J64/1000000000</f>
+        <f>$D$56*$D$24*J64/1E9</f>
         <v/>
       </c>
       <c r="K70" s="18">
-        <f>$D$56*$D$24*K64/1000000000</f>
+        <f>$D$56*$D$24*K64/1E9</f>
         <v/>
       </c>
       <c r="L70" s="18">
-        <f>$D$56*$D$24*L64/1000000000</f>
+        <f>$D$56*$D$24*L64/1E9</f>
         <v/>
       </c>
       <c r="M70" s="18">
-        <f>$D$56*$D$24*M64/1000000000</f>
+        <f>$D$56*$D$24*M64/1E9</f>
         <v/>
       </c>
       <c r="N70" s="18">
-        <f>$D$56*$D$24*N64/1000000000</f>
+        <f>$D$56*$D$24*N64/1E9</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,11 +19,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0_);(#,##0.0)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,21 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -117,12 +133,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +149,14 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -207,6 +231,261 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0">
+      <text>
+        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
+      <text>
+        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0">
+      <text>
+        <t>Availability for dispatch when called. Higher than CF because plant can run but chooses not to when uneconomic.</t>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0" shapeId="0">
+      <text>
+        <t>Unlike baseload, peakers run only during high-price hours. 400-800 hrs/yr typical. NOT capacity factor × 8760.</t>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="0" shapeId="0">
+      <text>
+        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0" shapeId="0">
+      <text>
+        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="0" shapeId="0">
+      <text>
+        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
+      </text>
+    </comment>
+    <comment ref="C44" authorId="0" shapeId="0">
+      <text>
+        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0">
+      <text>
+        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C47" authorId="0" shapeId="0">
+      <text>
+        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0" shapeId="0">
+      <text>
+        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="0" shapeId="0">
+      <text>
+        <t>Excludes land (~15% of EV). Depreciation creates tax shield, improves after-tax cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="C55" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
+      </text>
+    </comment>
+    <comment ref="C56" authorId="0" shapeId="0">
+      <text>
+        <t>CRITICAL: Use dispatch hours, NOT CF × 8760. Peakers run few hours but earn most revenue from capacity payments.</t>
+      </text>
+    </comment>
+    <comment ref="C63" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
+      </text>
+    </comment>
+    <comment ref="C67" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
+      </text>
+    </comment>
+    <comment ref="C70" authorId="0" shapeId="0">
+      <text>
+        <t>Peaker HR (10,000+) is worse than CCGT (7,000) because simple cycle. But low dispatch hours limit total fuel spend.</t>
+      </text>
+    </comment>
+    <comment ref="C75" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C80" authorId="0" shapeId="0">
+      <text>
+        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
+      </text>
+    </comment>
+    <comment ref="C81" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C83" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C84" authorId="0" shapeId="0">
+      <text>
+        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
+      </text>
+    </comment>
+    <comment ref="C85" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C87" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C89" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C91" authorId="0" shapeId="0">
+      <text>
+        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+      </text>
+    </comment>
+    <comment ref="C92" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C95" authorId="0" shapeId="0">
+      <text>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
+      </text>
+    </comment>
+    <comment ref="C97" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C103" authorId="0" shapeId="0">
+      <text>
+        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
+      </text>
+    </comment>
+    <comment ref="C108" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C109" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C126" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C127" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C131" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +867,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
       <c r="D3" s="7">
         <f>$D$17</f>
         <v/>
@@ -605,7 +888,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="D4" s="7">
         <f>E75</f>
         <v/>
@@ -622,7 +908,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
+      <c r="C5" s="6">
+        <f> EBITDA − Taxes</f>
+        <v/>
+      </c>
       <c r="D5" s="7">
         <f>AVERAGE(E81:K81)</f>
         <v/>
@@ -639,8 +928,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="8">
+      <c r="C6" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
         <f>MIN(E92:K92)</f>
         <v/>
       </c>
@@ -656,8 +948,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="9">
+      <c r="C7" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
         <f>D126</f>
         <v/>
       </c>
@@ -673,8 +968,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="8">
+      <c r="C8" s="6">
+        <f> Total In / Total Out</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
         <f>D127</f>
         <v/>
       </c>
@@ -690,8 +988,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
         <f>D131</f>
         <v/>
       </c>
@@ -749,7 +1050,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
@@ -811,7 +1115,7 @@
           <t>Legal, advisory, financing</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="26" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -831,7 +1135,7 @@
           <t>On exit year EBITDA</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="27" t="n">
         <v>7</v>
       </c>
     </row>
@@ -931,7 +1235,7 @@
           <t>For UCAP accreditation</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="26" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -951,7 +1255,7 @@
           <t>Unplanned downtime</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="26" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1071,7 +1375,7 @@
           <t>Applied to all prices/costs</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="26" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1211,7 +1515,7 @@
           <t>Debt / Entry EV (lower)</t>
         </is>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="26" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1231,7 +1535,7 @@
           <t>All-in borrowing cost</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D43" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -1291,7 +1595,7 @@
           <t>Lower for maint reserves</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="26" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1311,7 +1615,7 @@
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="27" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1351,7 +1655,7 @@
           <t>Blended federal + state</t>
         </is>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="D50" s="26" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1371,7 +1675,7 @@
           <t>% of EV for depreciation</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="26" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -1610,7 +1914,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Escalated</t>
+          <t>Nameplate MW</t>
         </is>
       </c>
       <c r="E63" s="18">
@@ -2113,7 +2417,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr"/>
+      <c r="C75" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="E75" s="7">
         <f>E68-E73</f>
         <v/>
@@ -2410,7 +2717,11 @@
         </is>
       </c>
       <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
@@ -2434,7 +2745,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr"/>
+      <c r="C84" s="6">
+        <f> Prior Yr End Bal</f>
+        <v/>
+      </c>
       <c r="E84" s="18">
         <f>$D$57</f>
         <v/>
@@ -2891,43 +3205,43 @@
           <t>CFADS / Debt Service</t>
         </is>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="24">
         <f>IF(E87&gt;0,E81/E87,0)</f>
         <v/>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="24">
         <f>IF(F87&gt;0,F81/F87,0)</f>
         <v/>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="24">
         <f>IF(G87&gt;0,G81/G87,0)</f>
         <v/>
       </c>
-      <c r="H92" s="8">
+      <c r="H92" s="24">
         <f>IF(H87&gt;0,H81/H87,0)</f>
         <v/>
       </c>
-      <c r="I92" s="8">
+      <c r="I92" s="24">
         <f>IF(I87&gt;0,I81/I87,0)</f>
         <v/>
       </c>
-      <c r="J92" s="8">
+      <c r="J92" s="24">
         <f>IF(J87&gt;0,J81/J87,0)</f>
         <v/>
       </c>
-      <c r="K92" s="8">
+      <c r="K92" s="24">
         <f>IF(K87&gt;0,K81/K87,0)</f>
         <v/>
       </c>
-      <c r="L92" s="8">
+      <c r="L92" s="24">
         <f>IF(L87&gt;0,L81/L87,0)</f>
         <v/>
       </c>
-      <c r="M92" s="8">
+      <c r="M92" s="24">
         <f>IF(M87&gt;0,M81/M87,0)</f>
         <v/>
       </c>
-      <c r="N92" s="8">
+      <c r="N92" s="24">
         <f>IF(N87&gt;0,N81/N87,0)</f>
         <v/>
       </c>
@@ -3493,7 +3807,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr"/>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>% of EV for legal, advisory</t>
+        </is>
+      </c>
       <c r="D108" s="18">
         <f>$D$17*$D$18</f>
         <v/>
@@ -3510,7 +3828,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr"/>
+      <c r="C109" s="6">
+        <f> Target − Beginning</f>
+        <v/>
+      </c>
       <c r="D109" s="18">
         <f>D95</f>
         <v/>
@@ -3802,8 +4123,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr"/>
-      <c r="D126" s="9">
+      <c r="C126" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D126" s="25">
         <f>IRR(D125:K125)</f>
         <v/>
       </c>
@@ -3824,7 +4148,7 @@
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D127" s="8">
+      <c r="D127" s="24">
         <f>SUMIF(D125:K125,"&gt;0")/ABS(D125)</f>
         <v/>
       </c>
@@ -3906,10 +4230,204 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr"/>
-      <c r="D131" s="9">
+      <c r="C131" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D131" s="25">
         <f>IRR(D130:K130)</f>
         <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Natural Gas Peaking Facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>• Acquire 180 MW simple-cycle peaker at $90mm ($500/kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>• Low dispatch (400 hrs/yr) but high capacity value</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>• Revenue weighted toward capacity payments (70%+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>• Target returns: 14-16% levered IRR, 2.0-2.2x MOIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>1. Capacity-weighted revenue model</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Peakers earn on reliability, not runtime. Low dispatch hours limit fuel cost exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>2. Grid reliability premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   As renewables penetrate, fast-start peakers become more valuable for grid stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>3. Lower capital intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Simple cycle costs $500/kW vs $1,400/kW for CCGT. Lower basis improves returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Risk | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Capacity price volatility | Long-term capacity contracts where available</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Start-cycle wear | Maintenance reserves; long-term service agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Renewable displacement | Battery storage competition in 5-10 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>FINANCIAL SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Entry EV: $90mm | Leverage: 40% | Min DSCR: 1.32x</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Levered IRR: 15.0% | MOIC: 2.1x</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,21 +52,6 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -120,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,10 +137,6 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -241,247 +221,112 @@
   <commentList>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C13" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C17" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0" shapeId="0">
-      <text>
-        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
-      </text>
-    </comment>
-    <comment ref="C23" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
-      </text>
-    </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
-      <text>
-        <t>Availability for dispatch when called. Higher than CF because plant can run but chooses not to when uneconomic.</t>
-      </text>
-    </comment>
-    <comment ref="C27" authorId="0" shapeId="0">
-      <text>
-        <t>Unlike baseload, peakers run only during high-price hours. 400-800 hrs/yr typical. NOT capacity factor × 8760.</t>
-      </text>
-    </comment>
-    <comment ref="C31" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
-      </text>
-    </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
-      <text>
-        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
-      </text>
-    </comment>
-    <comment ref="C39" authorId="0" shapeId="0">
-      <text>
-        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
-      </text>
-    </comment>
-    <comment ref="C42" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
-      </text>
-    </comment>
-    <comment ref="C43" authorId="0" shapeId="0">
-      <text>
-        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
-      </text>
-    </comment>
-    <comment ref="C44" authorId="0" shapeId="0">
-      <text>
-        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
-      </text>
-    </comment>
-    <comment ref="C45" authorId="0" shapeId="0">
-      <text>
-        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C46" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C47" authorId="0" shapeId="0">
       <text>
-        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
-      </text>
-    </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
-      <text>
-        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
-      </text>
-    </comment>
-    <comment ref="C51" authorId="0" shapeId="0">
-      <text>
-        <t>Excludes land (~15% of EV). Depreciation creates tax shield, improves after-tax cash flow.</t>
-      </text>
-    </comment>
-    <comment ref="C55" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
-      </text>
-    </comment>
-    <comment ref="C56" authorId="0" shapeId="0">
-      <text>
-        <t>CRITICAL: Use dispatch hours, NOT CF × 8760. Peakers run few hours but earn most revenue from capacity payments.</t>
-      </text>
-    </comment>
-    <comment ref="C63" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
-      </text>
-    </comment>
-    <comment ref="C67" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output. Peakers are smaller than baseload but valuable for reliability during peak demand.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C70" authorId="0" shapeId="0">
       <text>
-        <t>Peaker HR (10,000+) is worse than CCGT (7,000) because simple cycle. But low dispatch hours limit total fuel spend.</t>
+        <t>Largest variable cost for thermal plants. Divide by 1E9 to convert to $mm.</t>
       </text>
     </comment>
     <comment ref="C75" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
-      </text>
-    </comment>
-    <comment ref="C80" authorId="0" shapeId="0">
-      <text>
-        <t>Each start-stop cycle causes wear. Major maintenance every 5-7 years. Factor into cash flow timing.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C81" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C83" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C84" authorId="0" shapeId="0">
-      <text>
-        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
-      </text>
-    </comment>
-    <comment ref="C85" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C87" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C89" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C91" authorId="0" shapeId="0">
-      <text>
-        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C92" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
+        <t>Debt service using straight-line principal only. Used for DSRA to avoid circularity.</t>
       </text>
     </comment>
     <comment ref="C95" authorId="0" shapeId="0">
       <text>
-        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
-      </text>
-    </comment>
-    <comment ref="C97" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
-      </text>
-    </comment>
-    <comment ref="C103" authorId="0" shapeId="0">
-      <text>
-        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
-      </text>
-    </comment>
-    <comment ref="C108" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C109" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS to avoid circular reference.</t>
       </text>
     </comment>
     <comment ref="C126" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C127" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C131" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
   </commentList>
@@ -777,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -888,9 +733,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="D4" s="7">
         <f>E75</f>
@@ -908,9 +754,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6">
-        <f> EBITDA − Taxes</f>
-        <v/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA minus Taxes</t>
+        </is>
       </c>
       <c r="D5" s="7">
         <f>AVERAGE(E81:K81)</f>
@@ -928,9 +775,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D6" s="24">
         <f>MIN(E92:K92)</f>
@@ -948,9 +796,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D7" s="25">
         <f>D126</f>
@@ -968,9 +817,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6">
-        <f> Total In / Total Out</f>
-        <v/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Total In / Total Out</t>
+        </is>
       </c>
       <c r="D8" s="24">
         <f>D127</f>
@@ -988,9 +838,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D9" s="25">
         <f>D131</f>
@@ -1050,15 +901,18 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1159,6 +1013,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1279,6 +1134,7 @@
         <v>400</v>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
@@ -1379,6 +1235,7 @@
         <v>0.025</v>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
@@ -1479,6 +1336,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -1619,6 +1477,7 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -1699,6 +1558,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -1824,6 +1684,7 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
@@ -1914,7 +1775,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Nameplate MW</t>
+          <t>Escalated</t>
         </is>
       </c>
       <c r="E63" s="18">
@@ -2015,6 +1876,7 @@
         <v/>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -2182,6 +2044,7 @@
         <v/>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
@@ -2406,6 +2269,7 @@
         <v/>
       </c>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
@@ -2417,9 +2281,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C75" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="E75" s="7">
         <f>E68-E73</f>
@@ -2462,6 +2327,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
@@ -2710,6 +2576,7 @@
         <v/>
       </c>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
@@ -2719,7 +2586,7 @@
       <c r="B83" s="4" t="n"/>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>% of excess cash to prepay</t>
+          <t>MIN(Excess×%, Bal−Sched)</t>
         </is>
       </c>
       <c r="D83" s="4" t="n"/>
@@ -2745,10 +2612,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C84" s="6">
-        <f> Prior Yr End Bal</f>
-        <v/>
-      </c>
+      <c r="C84" s="6" t="inlineStr"/>
       <c r="E84" s="18">
         <f>$D$57</f>
         <v/>
@@ -3563,6 +3427,7 @@
         <v/>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
@@ -3750,6 +3615,7 @@
         <v/>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -3807,11 +3673,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>% of EV for legal, advisory</t>
-        </is>
-      </c>
+      <c r="C108" s="6" t="inlineStr"/>
       <c r="D108" s="18">
         <f>$D$17*$D$18</f>
         <v/>
@@ -3828,10 +3690,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C109" s="6">
-        <f> Target − Beginning</f>
-        <v/>
-      </c>
+      <c r="C109" s="6" t="inlineStr"/>
       <c r="D109" s="18">
         <f>D95</f>
         <v/>
@@ -3854,6 +3713,7 @@
         <v/>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" s="23" t="inlineStr">
         <is>
@@ -3931,6 +3791,7 @@
         <v/>
       </c>
     </row>
+    <row r="117"/>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
@@ -4035,6 +3896,7 @@
         <v/>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
@@ -4123,9 +3985,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C126" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D126" s="25">
         <f>IRR(D125:K125)</f>
@@ -4153,6 +4016,7 @@
         <v/>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" s="23" t="inlineStr">
         <is>
@@ -4230,207 +4094,46 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C131" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D131" s="25">
         <f>IRR(D130:K130)</f>
         <v/>
       </c>
     </row>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Natural Gas Peaking Facility</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>EXECUTIVE SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>• Acquire 180 MW simple-cycle peaker at $90mm ($500/kW)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>• Low dispatch (400 hrs/yr) but high capacity value</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>• Revenue weighted toward capacity payments (70%+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>• Target returns: 14-16% levered IRR, 2.0-2.2x MOIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>1. Capacity-weighted revenue model</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Peakers earn on reliability, not runtime. Low dispatch hours limit fuel cost exposure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>2. Grid reliability premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   As renewables penetrate, fast-start peakers become more valuable for grid stability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>3. Lower capital intensity</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Simple cycle costs $500/kW vs $1,400/kW for CCGT. Lower basis improves returns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>Risk | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Capacity price volatility | Long-term capacity contracts where available</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>Start-cycle wear | Maintenance reserves; long-term service agreement</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>Renewable displacement | Battery storage competition in 5-10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>FINANCIAL SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>Entry EV: $90mm | Leverage: 40% | Min DSCR: 1.32x</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>Levered IRR: 15.0% | MOIC: 2.1x</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,20 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,6 +152,15 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -622,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -911,8 +935,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1035,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1134,7 +1155,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
@@ -1235,7 +1255,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
@@ -1336,7 +1355,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1495,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -1558,7 +1575,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -1684,7 +1700,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1891,6 @@
         <v/>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -2044,7 +2058,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
@@ -2269,7 +2282,6 @@
         <v/>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
@@ -2327,7 +2339,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
@@ -2576,7 +2587,6 @@
         <v/>
       </c>
     </row>
-    <row r="82"/>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
@@ -3427,7 +3437,6 @@
         <v/>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
@@ -3615,7 +3624,6 @@
         <v/>
       </c>
     </row>
-    <row r="104"/>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -3713,7 +3721,6 @@
         <v/>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" s="23" t="inlineStr">
         <is>
@@ -3791,7 +3798,6 @@
         <v/>
       </c>
     </row>
-    <row r="117"/>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
@@ -3896,7 +3902,6 @@
         <v/>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
@@ -4016,7 +4021,6 @@
         <v/>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="23" t="inlineStr">
         <is>
@@ -4104,36 +4108,269 @@
         <v/>
       </c>
     </row>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>PROJECT PHOENIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>200 MW Simple Cycle Peaker – NYISO Zone J</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $110mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>• NYISO Zone J capacity scarcity drives premium capacity prices ($60/kW-yr vs $40 market average)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>• Fast-start capability (10-minute dispatch) positions asset for ancillary services revenue growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>• Conservative 30% leverage with 50% sweep retains cash for major maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>• Exit to utility seeking reliability assets in constrained zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why dispatch hours instead of capacity factor?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>A: Peakers run only during peak demand (~400 hours). Using CF × 8,760 would overstate generation by 10x. This is the most common modeling error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Q: What if the peaker never dispatches?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>A: Still receive capacity payments (65% of revenue). Energy revenue is upside, not base case. Worst case = capacity-only returns still above hurdle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why 50% sweep vs 75% for CCGT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>A: Need to retain cash for major maintenance (HGP every 5 years = $4mm). Higher sweep would require external funding for maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Q: How does battery storage affect peakers?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>A: 4-hour batteries handle daily peaks. Peakers needed for multi-day events, extreme weather, renewable droughts. Complementary, not substitutive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>Entry EV | $110mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 8.5x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Leverage | 30% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Levered IRR | 16.8% | 12.5% | 21.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>MOIC | 1.95x | 1.65x | 2.25x</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Min DSCR | 1.55x | 1.35x | 1.75x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Unlevered IRR | 13.2% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Capacity price decline | Medium | Zone J structural scarcity; 3-year forward locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Major maintenance timing | Medium | HGP in Y5 budgeted; LTSA provides cost certainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>Limited dispatch hours | Low | Capacity revenue = 65% of total; energy is upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Battery competition | Medium | Batteries complement, not replace – need gas for multi-day events</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +69,9 @@
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,6 +166,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -646,6 +652,427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Peaker - INTUITION MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>WHAT THIS MODEL DOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Simple Cycle - Fast-start for peak hours. Revenue weighted to capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>KEY VALUE DRIVERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1. Capacity Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2. Starts/Runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3. Heat Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>DEBT STRUCTURE RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>50% sweep with maintenance reserves.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: Peaker ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>200 MW peaker in NYISO Zone J at $95mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>PROJECT PHOENIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>200 MW Simple Cycle Peaker – NYISO Zone J</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $110mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>• NYISO Zone J capacity scarcity drives premium capacity prices ($60/kW-yr vs $40 market average)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>• Fast-start capability (10-minute dispatch) positions asset for ancillary services revenue growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>• Conservative 30% leverage with 50% sweep retains cash for major maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>• Exit to utility seeking reliability assets in constrained zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why dispatch hours instead of capacity factor?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>A: Peakers run only during peak demand (~400 hours). Using CF × 8,760 would overstate generation by 10x. This is the most common modeling error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Q: What if the peaker never dispatches?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>A: Still receive capacity payments (65% of revenue). Energy revenue is upside, not base case. Worst case = capacity-only returns still above hurdle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why 50% sweep vs 75% for CCGT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>A: Need to retain cash for major maintenance (HGP every 5 years = $4mm). Higher sweep would require external funding for maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Q: How does battery storage affect peakers?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>A: 4-hour batteries handle daily peaks. Peakers needed for multi-day events, extreme weather, renewable droughts. Complementary, not substitutive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>Entry EV | $110mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 8.5x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Leverage | 30% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Levered IRR | 16.8% | 12.5% | 21.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>MOIC | 1.95x | 1.65x | 2.25x</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Min DSCR | 1.55x | 1.35x | 1.75x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Unlevered IRR | 13.2% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Capacity price decline | Medium | Zone J structural scarcity; 3-year forward locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Major maintenance timing | Medium | HGP in Y5 budgeted; LTSA provides cost certainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>Limited dispatch hours | Low | Capacity revenue = 65% of total; energy is upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Battery competition | Medium | Batteries complement, not replace – need gas for multi-day events</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -805,7 +1232,7 @@
         </is>
       </c>
       <c r="D6" s="24">
-        <f>MIN(E92:K92)</f>
+        <f>IF(COUNTIF(E92:K92,"&gt;0")&gt;0,MINIFS(E92:K92,E92:K92,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -4112,265 +4539,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>PROJECT PHOENIX</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>200 MW Simple Cycle Peaker – NYISO Zone J</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION: Proceed to final bid at $110mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>KEY METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>• NYISO Zone J capacity scarcity drives premium capacity prices ($60/kW-yr vs $40 market average)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>• Fast-start capability (10-minute dispatch) positions asset for ancillary services revenue growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>• Conservative 30% leverage with 50% sweep retains cash for major maintenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>• Exit to utility seeking reliability assets in constrained zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>ANTICIPATED IC Q&amp;A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>Q: Why dispatch hours instead of capacity factor?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>A: Peakers run only during peak demand (~400 hours). Using CF × 8,760 would overstate generation by 10x. This is the most common modeling error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>Q: What if the peaker never dispatches?</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>A: Still receive capacity payments (65% of revenue). Energy revenue is upside, not base case. Worst case = capacity-only returns still above hurdle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>Q: Why 50% sweep vs 75% for CCGT?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>A: Need to retain cash for major maintenance (HGP every 5 years = $4mm). Higher sweep would require external funding for maintenance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>Q: How does battery storage affect peakers?</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>A: 4-hour batteries handle daily peaks. Peakers needed for multi-day events, extreme weather, renewable droughts. Complementary, not substitutive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>Metric | Base Case | Downside | Upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>Entry EV | $110mm | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>Entry Multiple | 8.5x Y1 EBITDA | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>Leverage | 30% | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>Levered IRR | 16.8% | 12.5% | 21.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>MOIC | 1.95x | 1.65x | 2.25x</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Min DSCR | 1.55x | 1.35x | 1.75x</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>Unlevered IRR | 13.2% | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="28" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>Risk | Probability | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>Capacity price decline | Medium | Zone J structural scarcity; 3-year forward locked</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>Major maintenance timing | Medium | HGP in Y5 budgeted; LTSA provides cost certainty</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>Limited dispatch hours | Low | Capacity revenue = 65% of total; energy is upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>Battery competition | Medium | Batteries complement, not replace – need gas for multi-day events</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
     </font>
   </fonts>
   <fills count="6">
@@ -124,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,6 +171,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -652,72 +663,545 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Peaker - INTUITION MAP</t>
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>WHAT THIS MODEL DOES</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: SIMPLE CYCLE GAS TURBINE (PEAKER) ACQUISITION</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Simple Cycle - Fast-start for peak hours. Revenue weighted to capacity.</t>
-        </is>
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>KEY VALUE DRIVERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1. Capacity Price</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2. Starts/Runtime</t>
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. Heat Rate</t>
+          <t>Year 0 (2025): Transaction close Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): First full year; start-based maintenance tracking</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>DEBT STRUCTURE RATIONALE</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 5 (2030): Potential hot gas path inspection</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>50% sweep with maintenance reserves.</t>
+          <t>Year 7 (2032): Target exit / debt maturity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Year 10 (2035): Model horizon end</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating a 200 MW simple-cycle gas
+turbine peaking facility in NYISO Zone J (New York City). The plant is 8 years
+old with approximately 2,500 equivalent operating starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>Zone J has strong capacity prices due to transmission constraints. The facility
+provides reliability during summer peaks and winter cold snaps. It operates
+approximately 400 hours per year with revenue heavily weighted to capacity
+payments (~70% of total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>The 10,500 Btu/kWh heat rate is higher than CCGT but acceptable for peaking
+duty. Recent planning studies indicate potential capacity additions over 3-5
+years including offshore wind and battery storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>The seller is asking $95mm with bids due by January 31, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Capacity Price: Peakers earn 70%+ of revenue from capacity auctions</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Dispatch Hours: Annual run hours drive energy revenue and fuel cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Starts: Each start costs money and accelerates maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>* Availability: UCAP derate risk if availability drops below threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR PEAKERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCE: Generation = Capacity x Dispatch Hours x Availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>(NOT Capacity x CF x 8,760 like CCGT!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capacity: 200 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Heat Rate: 10,500 Btu/kWh (worse than CCGT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Availability: 94% (mechanical availability, not CF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - FOR: 5% (for UCAP derate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Dispatch Hours: 400 hrs/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Starts per Year: ~50-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>2. BUILD GENERATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Generation = Capacity x Dispatch Hours x Availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   = 200 MW x 400 hrs x 0.94 = 75,200 MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>3. CAPACITY REVENUE IS DOMINANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   UCAP = Capacity x (1 - FOR) = 200 x 0.95 = 190 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Capacity Revenue = UCAP x $/kW-yr x 1000 / 1E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Verify: Capacity should be ~70% of total revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="33" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="33" t="inlineStr">
+        <is>
+          <t>4. DEBT STRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   50% cash sweep (vs 75% for CCGT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Preserve flexibility for lumpy maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Peaker cash flows more volatile</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Same approach as CCGT - use Scheduled DS for DSRA Target to avoid circularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A. Ancillary Services Revenue:</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Spinning/non-spinning reserves</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Can be 10-15% of total revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B. Black Start Capability:</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Premium for grid restoration</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Adds contracted revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C. Capacity Contract vs Merchant:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Different risk profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Affects debt sizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1. Capacity revenue should be 60-75% of total (peaker profile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2. Generation = Dispatch Hours x Availability (NOT CF x 8760)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3. Energy margin may be negative in some hours (heat rate penalty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4. DSCR &gt;= 1.25x during debt tenor</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="34" t="inlineStr">
+        <is>
+          <t>* Capacity is ~70% of revenue - focus sensitivity there</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="34" t="inlineStr">
+        <is>
+          <t>* Each start costs money plus accelerates maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="34" t="inlineStr">
+        <is>
+          <t>* Zone J premium can erode if storage/transmission added</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="34" t="inlineStr">
+        <is>
+          <t>* Don't model generation as CF x 8760 - use Dispatch Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="31" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Q: How would 100 MW of battery storage in Zone J affect capacity prices?</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Q: Walk me through starts-based vs hours-based maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Q: Why is availability so critical for peaker economics?</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Q: How would you model the revenue mix between capacity and energy?</t>
         </is>
       </c>
     </row>
@@ -1098,38 +1582,60 @@
           <t>Peaker Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="32" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="32" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="32" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="32" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="32" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="32" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="32" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="32" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="32" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="32" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +106,14 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -157,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,6 +238,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3324,7 +3334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3445,6 +3455,11 @@
         <f>$D$17</f>
         <v/>
       </c>
+      <c r="M3" s="54" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3465,6 +3480,11 @@
       <c r="D4" s="7">
         <f>E75</f>
         <v/>
+      </c>
+      <c r="M4" s="55" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3476,6 +3496,11 @@
       <c r="B5" s="46" t="n"/>
       <c r="C5" s="46" t="n"/>
       <c r="D5" s="46" t="n"/>
+      <c r="M5" s="55" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="46" t="n"/>
@@ -4938,17 +4963,7 @@
           <t>[WHAT] Spark Spread = Power Price - (Plant HR × Gas / 1000)
 [WHY] Gross margin per MWh after fuel. Core driver of thermal profitability.
 [RMHR EQUIVALENCE - For Interview Discussion]
-Traders express this as "Market Heat Rate":
-  RMHR = Power / Gas × 1000
-  If RMHR &gt; Plant HR → "In the money" → Dispatch
-Spark Spread = (RMHR - Plant HR) × Gas / 1000
-Same math, different framing. Use Spark Spread in model (simpler).
-[EXAMPLE] Power=$50, Gas=$5, HR=7000
-  RMHR = 50/5 × 1000 = 10,000 Btu/kWh
-  Spread = 10,000 - 7,000 = 3,000 Btu/kWh
-  Spark = 3,000 × $5 / 1000 = $15/MWh ✓
-  (Or directly: $50 - 7×$5 = $15/MWh)
-[UNITS] $/MWh - (Btu/kWh × $/MMBtu / 1000) = $/MWh ✓</t>
+Traders express this as "Market Heat Rate":</t>
         </is>
       </c>
       <c r="E82" s="53">
@@ -6994,14 +7009,6 @@
         <v/>
       </c>
     </row>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -7025,7 +7032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7432,8 +7439,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -7534,7 +7539,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -7655,7 +7659,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -7756,7 +7759,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -7857,7 +7859,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -7998,7 +7999,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -8079,7 +8079,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
@@ -8205,7 +8204,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
@@ -8397,7 +8395,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
@@ -8565,7 +8562,6 @@
         <v/>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
@@ -8860,7 +8856,6 @@
         <v/>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
@@ -8918,7 +8913,6 @@
         <v/>
       </c>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
@@ -9167,7 +9161,6 @@
         <v/>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -10018,7 +10011,6 @@
         <v/>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
@@ -10206,7 +10198,6 @@
         <v/>
       </c>
     </row>
-    <row r="116"/>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
@@ -10343,8 +10334,6 @@
         </is>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127"/>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
@@ -10362,7 +10351,6 @@
         <v/>
       </c>
     </row>
-    <row r="129"/>
     <row r="130">
       <c r="A130" s="23" t="inlineStr">
         <is>
@@ -10440,7 +10428,6 @@
         <v/>
       </c>
     </row>
-    <row r="135"/>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
@@ -10545,7 +10532,6 @@
         <v/>
       </c>
     </row>
-    <row r="141"/>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
@@ -10665,7 +10651,6 @@
         <v/>
       </c>
     </row>
-    <row r="146"/>
     <row r="147">
       <c r="A147" s="23" t="inlineStr">
         <is>
@@ -10753,8 +10738,6 @@
         <v/>
       </c>
     </row>
-    <row r="150"/>
-    <row r="151"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="D3" s="7">
-        <f>$D$17</f>
+        <f>$D$28</f>
         <v/>
       </c>
       <c r="M3" s="54" t="inlineStr">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="D4" s="7">
-        <f>E75</f>
+        <f>E87</f>
         <v/>
       </c>
       <c r="M4" s="55" t="inlineStr">
@@ -3756,8 +3756,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -3858,7 +3856,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -3979,7 +3976,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -4080,7 +4076,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -4181,7 +4176,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -4322,7 +4316,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -4403,7 +4396,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
@@ -4441,7 +4433,7 @@
         </is>
       </c>
       <c r="D66" s="16">
-        <f>$D$23*(1-$D$26)</f>
+        <f>$D$34*(1-$D$37)</f>
         <v/>
       </c>
     </row>
@@ -4462,7 +4454,7 @@
         </is>
       </c>
       <c r="D67" s="17">
-        <f>$D$23*$D$27*$D$25</f>
+        <f>$D$34*$D$38*$D$36</f>
         <v/>
       </c>
     </row>
@@ -4483,7 +4475,7 @@
         </is>
       </c>
       <c r="D68" s="18">
-        <f>$D$17*$D$42</f>
+        <f>$D$28*$D$53</f>
         <v/>
       </c>
     </row>
@@ -4504,7 +4496,7 @@
         </is>
       </c>
       <c r="D69" s="18">
-        <f>$D$17*$D$51/$D$52</f>
+        <f>$D$28*$D$62/$D$63</f>
         <v/>
       </c>
     </row>
@@ -4525,11 +4517,10 @@
         </is>
       </c>
       <c r="D70" s="18">
-        <f>$D$57/$D$44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71"/>
+        <f>$D$68/$D$55</f>
+        <v/>
+      </c>
+    </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
@@ -4567,43 +4558,43 @@
         </is>
       </c>
       <c r="E73" s="18">
-        <f>$D$30*(1+$D$33)^(1-1)</f>
+        <f>$D$41*(1+$D$44)^(1-1)</f>
         <v/>
       </c>
       <c r="F73" s="18">
-        <f>$D$30*(1+$D$33)^(2-1)</f>
+        <f>$D$41*(1+$D$44)^(2-1)</f>
         <v/>
       </c>
       <c r="G73" s="18">
-        <f>$D$30*(1+$D$33)^(3-1)</f>
+        <f>$D$41*(1+$D$44)^(3-1)</f>
         <v/>
       </c>
       <c r="H73" s="18">
-        <f>$D$30*(1+$D$33)^(4-1)</f>
+        <f>$D$41*(1+$D$44)^(4-1)</f>
         <v/>
       </c>
       <c r="I73" s="18">
-        <f>$D$30*(1+$D$33)^(5-1)</f>
+        <f>$D$41*(1+$D$44)^(5-1)</f>
         <v/>
       </c>
       <c r="J73" s="18">
-        <f>$D$30*(1+$D$33)^(6-1)</f>
+        <f>$D$41*(1+$D$44)^(6-1)</f>
         <v/>
       </c>
       <c r="K73" s="18">
-        <f>$D$30*(1+$D$33)^(7-1)</f>
+        <f>$D$41*(1+$D$44)^(7-1)</f>
         <v/>
       </c>
       <c r="L73" s="18">
-        <f>$D$30*(1+$D$33)^(8-1)</f>
+        <f>$D$41*(1+$D$44)^(8-1)</f>
         <v/>
       </c>
       <c r="M73" s="18">
-        <f>$D$30*(1+$D$33)^(9-1)</f>
+        <f>$D$41*(1+$D$44)^(9-1)</f>
         <v/>
       </c>
       <c r="N73" s="18">
-        <f>$D$30*(1+$D$33)^(10-1)</f>
+        <f>$D$41*(1+$D$44)^(10-1)</f>
         <v/>
       </c>
     </row>
@@ -4624,43 +4615,43 @@
         </is>
       </c>
       <c r="E74" s="18">
-        <f>$D$31*(1+$D$33)^(1-1)</f>
+        <f>$D$42*(1+$D$44)^(1-1)</f>
         <v/>
       </c>
       <c r="F74" s="18">
-        <f>$D$31*(1+$D$33)^(2-1)</f>
+        <f>$D$42*(1+$D$44)^(2-1)</f>
         <v/>
       </c>
       <c r="G74" s="18">
-        <f>$D$31*(1+$D$33)^(3-1)</f>
+        <f>$D$42*(1+$D$44)^(3-1)</f>
         <v/>
       </c>
       <c r="H74" s="18">
-        <f>$D$31*(1+$D$33)^(4-1)</f>
+        <f>$D$42*(1+$D$44)^(4-1)</f>
         <v/>
       </c>
       <c r="I74" s="18">
-        <f>$D$31*(1+$D$33)^(5-1)</f>
+        <f>$D$42*(1+$D$44)^(5-1)</f>
         <v/>
       </c>
       <c r="J74" s="18">
-        <f>$D$31*(1+$D$33)^(6-1)</f>
+        <f>$D$42*(1+$D$44)^(6-1)</f>
         <v/>
       </c>
       <c r="K74" s="18">
-        <f>$D$31*(1+$D$33)^(7-1)</f>
+        <f>$D$42*(1+$D$44)^(7-1)</f>
         <v/>
       </c>
       <c r="L74" s="18">
-        <f>$D$31*(1+$D$33)^(8-1)</f>
+        <f>$D$42*(1+$D$44)^(8-1)</f>
         <v/>
       </c>
       <c r="M74" s="18">
-        <f>$D$31*(1+$D$33)^(9-1)</f>
+        <f>$D$42*(1+$D$44)^(9-1)</f>
         <v/>
       </c>
       <c r="N74" s="18">
-        <f>$D$31*(1+$D$33)^(10-1)</f>
+        <f>$D$42*(1+$D$44)^(10-1)</f>
         <v/>
       </c>
     </row>
@@ -4681,47 +4672,46 @@
         </is>
       </c>
       <c r="E75" s="19">
-        <f>$D$32*(1+$D$33)^(1-1)</f>
+        <f>$D$43*(1+$D$44)^(1-1)</f>
         <v/>
       </c>
       <c r="F75" s="19">
-        <f>$D$32*(1+$D$33)^(2-1)</f>
+        <f>$D$43*(1+$D$44)^(2-1)</f>
         <v/>
       </c>
       <c r="G75" s="19">
-        <f>$D$32*(1+$D$33)^(3-1)</f>
+        <f>$D$43*(1+$D$44)^(3-1)</f>
         <v/>
       </c>
       <c r="H75" s="19">
-        <f>$D$32*(1+$D$33)^(4-1)</f>
+        <f>$D$43*(1+$D$44)^(4-1)</f>
         <v/>
       </c>
       <c r="I75" s="19">
-        <f>$D$32*(1+$D$33)^(5-1)</f>
+        <f>$D$43*(1+$D$44)^(5-1)</f>
         <v/>
       </c>
       <c r="J75" s="19">
-        <f>$D$32*(1+$D$33)^(6-1)</f>
+        <f>$D$43*(1+$D$44)^(6-1)</f>
         <v/>
       </c>
       <c r="K75" s="19">
-        <f>$D$32*(1+$D$33)^(7-1)</f>
+        <f>$D$43*(1+$D$44)^(7-1)</f>
         <v/>
       </c>
       <c r="L75" s="19">
-        <f>$D$32*(1+$D$33)^(8-1)</f>
+        <f>$D$43*(1+$D$44)^(8-1)</f>
         <v/>
       </c>
       <c r="M75" s="19">
-        <f>$D$32*(1+$D$33)^(9-1)</f>
+        <f>$D$43*(1+$D$44)^(9-1)</f>
         <v/>
       </c>
       <c r="N75" s="19">
-        <f>$D$32*(1+$D$33)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76"/>
+        <f>$D$43*(1+$D$44)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
@@ -4739,43 +4729,43 @@
         </is>
       </c>
       <c r="E77" s="18">
-        <f>$D$56*E62/1000000</f>
+        <f>$D$67*E73/1000000</f>
         <v/>
       </c>
       <c r="F77" s="18">
-        <f>$D$56*F62/1000000</f>
+        <f>$D$67*F73/1000000</f>
         <v/>
       </c>
       <c r="G77" s="18">
-        <f>$D$56*G62/1000000</f>
+        <f>$D$67*G73/1000000</f>
         <v/>
       </c>
       <c r="H77" s="18">
-        <f>$D$56*H62/1000000</f>
+        <f>$D$67*H73/1000000</f>
         <v/>
       </c>
       <c r="I77" s="18">
-        <f>$D$56*I62/1000000</f>
+        <f>$D$67*I73/1000000</f>
         <v/>
       </c>
       <c r="J77" s="18">
-        <f>$D$56*J62/1000000</f>
+        <f>$D$67*J73/1000000</f>
         <v/>
       </c>
       <c r="K77" s="18">
-        <f>$D$56*K62/1000000</f>
+        <f>$D$67*K73/1000000</f>
         <v/>
       </c>
       <c r="L77" s="18">
-        <f>$D$56*L62/1000000</f>
+        <f>$D$67*L73/1000000</f>
         <v/>
       </c>
       <c r="M77" s="18">
-        <f>$D$56*M62/1000000</f>
+        <f>$D$67*M73/1000000</f>
         <v/>
       </c>
       <c r="N77" s="18">
-        <f>$D$56*N62/1000000</f>
+        <f>$D$67*N73/1000000</f>
         <v/>
       </c>
     </row>
@@ -4796,43 +4786,43 @@
         </is>
       </c>
       <c r="E78" s="18">
-        <f>$D$55*E63*1000/1000000</f>
+        <f>$D$34*E74*1000/1000000</f>
         <v/>
       </c>
       <c r="F78" s="18">
-        <f>$D$55*F63*1000/1000000</f>
+        <f>$D$34*F74*1000/1000000</f>
         <v/>
       </c>
       <c r="G78" s="18">
-        <f>$D$55*G63*1000/1000000</f>
+        <f>$D$34*G74*1000/1000000</f>
         <v/>
       </c>
       <c r="H78" s="18">
-        <f>$D$55*H63*1000/1000000</f>
+        <f>$D$34*H74*1000/1000000</f>
         <v/>
       </c>
       <c r="I78" s="18">
-        <f>$D$55*I63*1000/1000000</f>
+        <f>$D$34*I74*1000/1000000</f>
         <v/>
       </c>
       <c r="J78" s="18">
-        <f>$D$55*J63*1000/1000000</f>
+        <f>$D$34*J74*1000/1000000</f>
         <v/>
       </c>
       <c r="K78" s="18">
-        <f>$D$55*K63*1000/1000000</f>
+        <f>$D$34*K74*1000/1000000</f>
         <v/>
       </c>
       <c r="L78" s="18">
-        <f>$D$55*L63*1000/1000000</f>
+        <f>$D$34*L74*1000/1000000</f>
         <v/>
       </c>
       <c r="M78" s="18">
-        <f>$D$55*M63*1000/1000000</f>
+        <f>$D$34*M74*1000/1000000</f>
         <v/>
       </c>
       <c r="N78" s="18">
-        <f>$D$55*N63*1000/1000000</f>
+        <f>$D$34*N74*1000/1000000</f>
         <v/>
       </c>
     </row>
@@ -4849,47 +4839,46 @@
       </c>
       <c r="C79" s="6" t="inlineStr"/>
       <c r="E79" s="20">
-        <f>E66+E67</f>
+        <f>E77+E78</f>
         <v/>
       </c>
       <c r="F79" s="20">
-        <f>F66+F67</f>
+        <f>F77+F78</f>
         <v/>
       </c>
       <c r="G79" s="20">
-        <f>G66+G67</f>
+        <f>G77+G78</f>
         <v/>
       </c>
       <c r="H79" s="20">
-        <f>H66+H67</f>
+        <f>H77+H78</f>
         <v/>
       </c>
       <c r="I79" s="20">
-        <f>I66+I67</f>
+        <f>I77+I78</f>
         <v/>
       </c>
       <c r="J79" s="20">
-        <f>J66+J67</f>
+        <f>J77+J78</f>
         <v/>
       </c>
       <c r="K79" s="20">
-        <f>K66+K67</f>
+        <f>K77+K78</f>
         <v/>
       </c>
       <c r="L79" s="20">
-        <f>L66+L67</f>
+        <f>L77+L78</f>
         <v/>
       </c>
       <c r="M79" s="20">
-        <f>M66+M67</f>
+        <f>M77+M78</f>
         <v/>
       </c>
       <c r="N79" s="20">
-        <f>N66+N67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80"/>
+        <f>N77+N78</f>
+        <v/>
+      </c>
+    </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
@@ -4907,43 +4896,43 @@
         </is>
       </c>
       <c r="E81" s="18">
-        <f>$D$56*$D$24*E64/1E9</f>
+        <f>$D$67*$D$35*E75/1000000000</f>
         <v/>
       </c>
       <c r="F81" s="18">
-        <f>$D$56*$D$24*F64/1E9</f>
+        <f>$D$67*$D$35*F75/1000000000</f>
         <v/>
       </c>
       <c r="G81" s="18">
-        <f>$D$56*$D$24*G64/1E9</f>
+        <f>$D$67*$D$35*G75/1000000000</f>
         <v/>
       </c>
       <c r="H81" s="18">
-        <f>$D$56*$D$24*H64/1E9</f>
+        <f>$D$67*$D$35*H75/1000000000</f>
         <v/>
       </c>
       <c r="I81" s="18">
-        <f>$D$56*$D$24*I64/1E9</f>
+        <f>$D$67*$D$35*I75/1000000000</f>
         <v/>
       </c>
       <c r="J81" s="18">
-        <f>$D$56*$D$24*J64/1E9</f>
+        <f>$D$67*$D$35*J75/1000000000</f>
         <v/>
       </c>
       <c r="K81" s="18">
-        <f>$D$56*$D$24*K64/1E9</f>
+        <f>$D$67*$D$35*K75/1000000000</f>
         <v/>
       </c>
       <c r="L81" s="18">
-        <f>$D$56*$D$24*L64/1E9</f>
+        <f>$D$67*$D$35*L75/1000000000</f>
         <v/>
       </c>
       <c r="M81" s="18">
-        <f>$D$56*$D$24*M64/1E9</f>
+        <f>$D$67*$D$35*M75/1000000000</f>
         <v/>
       </c>
       <c r="N81" s="18">
-        <f>$D$56*$D$24*N64/1E9</f>
+        <f>$D$67*$D$35*N75/1000000000</f>
         <v/>
       </c>
     </row>
@@ -4967,43 +4956,43 @@
         </is>
       </c>
       <c r="E82" s="53">
-        <f>E72-($D$34/1000)*E74</f>
+        <f>E73-($D$35/1000)*E75</f>
         <v/>
       </c>
       <c r="F82" s="53">
-        <f>F72-($D$34/1000)*F74</f>
+        <f>F73-($D$35/1000)*F75</f>
         <v/>
       </c>
       <c r="G82" s="53">
-        <f>G72-($D$34/1000)*G74</f>
+        <f>G73-($D$35/1000)*G75</f>
         <v/>
       </c>
       <c r="H82" s="53">
-        <f>H72-($D$34/1000)*H74</f>
+        <f>H73-($D$35/1000)*H75</f>
         <v/>
       </c>
       <c r="I82" s="53">
-        <f>I72-($D$34/1000)*I74</f>
+        <f>I73-($D$35/1000)*I75</f>
         <v/>
       </c>
       <c r="J82" s="53">
-        <f>J72-($D$34/1000)*J74</f>
+        <f>J73-($D$35/1000)*J75</f>
         <v/>
       </c>
       <c r="K82" s="53">
-        <f>K72-($D$34/1000)*K74</f>
+        <f>K73-($D$35/1000)*K75</f>
         <v/>
       </c>
       <c r="L82" s="53">
-        <f>L72-($D$34/1000)*L74</f>
+        <f>L73-($D$35/1000)*L75</f>
         <v/>
       </c>
       <c r="M82" s="53">
-        <f>M72-($D$34/1000)*M74</f>
+        <f>M73-($D$35/1000)*M75</f>
         <v/>
       </c>
       <c r="N82" s="53">
-        <f>N72-($D$34/1000)*N74</f>
+        <f>N73-($D$35/1000)*N75</f>
         <v/>
       </c>
     </row>
@@ -5024,43 +5013,43 @@
         </is>
       </c>
       <c r="E83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="F83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="G83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="H83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="I83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="J83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="K83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="L83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="M83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
       <c r="N83" s="18">
-        <f>$D$56*$D$36/1000000</f>
+        <f>$D$67*$D$47/1000000</f>
         <v/>
       </c>
     </row>
@@ -5081,43 +5070,43 @@
         </is>
       </c>
       <c r="E84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(1-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="F84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(2-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="G84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(3-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="H84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(4-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="I84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(5-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="J84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(6-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="K84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(7-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="L84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(8-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="M84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(9-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
       <c r="N84" s="18">
-        <f>$D$23*$D$37*(1+$D$33)^(10-1)*1000/1000000</f>
+        <f>$D$34*$D$48*1000/1000000</f>
         <v/>
       </c>
     </row>
@@ -5134,47 +5123,46 @@
       </c>
       <c r="C85" s="6" t="inlineStr"/>
       <c r="E85" s="18">
-        <f>E70+E71+E72</f>
+        <f>E81+E83+E84</f>
         <v/>
       </c>
       <c r="F85" s="18">
-        <f>F70+F71+F72</f>
+        <f>F81+F83+F84</f>
         <v/>
       </c>
       <c r="G85" s="18">
-        <f>G70+G71+G72</f>
+        <f>G81+G83+G84</f>
         <v/>
       </c>
       <c r="H85" s="18">
-        <f>H70+H71+H72</f>
+        <f>H81+H83+H84</f>
         <v/>
       </c>
       <c r="I85" s="18">
-        <f>I70+I71+I72</f>
+        <f>I81+I83+I84</f>
         <v/>
       </c>
       <c r="J85" s="18">
-        <f>J70+J71+J72</f>
+        <f>J81+J83+J84</f>
         <v/>
       </c>
       <c r="K85" s="18">
-        <f>K70+K71+K72</f>
+        <f>K81+K83+K84</f>
         <v/>
       </c>
       <c r="L85" s="18">
-        <f>L70+L71+L72</f>
+        <f>L81+L83+L84</f>
         <v/>
       </c>
       <c r="M85" s="18">
-        <f>M70+M71+M72</f>
+        <f>M81+M83+M84</f>
         <v/>
       </c>
       <c r="N85" s="18">
-        <f>N70+N71+N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86"/>
+        <f>N81+N83+N84</f>
+        <v/>
+      </c>
+    </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
@@ -5192,47 +5180,46 @@
         </is>
       </c>
       <c r="E87" s="7">
-        <f>E68-E73</f>
+        <f>E79-E85</f>
         <v/>
       </c>
       <c r="F87" s="7">
-        <f>F68-F73</f>
+        <f>F79-F85</f>
         <v/>
       </c>
       <c r="G87" s="7">
-        <f>G68-G73</f>
+        <f>G79-G85</f>
         <v/>
       </c>
       <c r="H87" s="7">
-        <f>H68-H73</f>
+        <f>H79-H85</f>
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>I68-I73</f>
+        <f>I79-I85</f>
         <v/>
       </c>
       <c r="J87" s="7">
-        <f>J68-J73</f>
+        <f>J79-J85</f>
         <v/>
       </c>
       <c r="K87" s="7">
-        <f>K68-K73</f>
+        <f>K79-K85</f>
         <v/>
       </c>
       <c r="L87" s="7">
-        <f>L68-L73</f>
+        <f>L79-L85</f>
         <v/>
       </c>
       <c r="M87" s="7">
-        <f>M68-M73</f>
+        <f>M79-M85</f>
         <v/>
       </c>
       <c r="N87" s="7">
-        <f>N68-N73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88"/>
+        <f>N79-N85</f>
+        <v/>
+      </c>
+    </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
@@ -5270,43 +5257,43 @@
         </is>
       </c>
       <c r="E90" s="18">
-        <f>E75-$D$58</f>
+        <f>E87-$D$69</f>
         <v/>
       </c>
       <c r="F90" s="18">
-        <f>F75-$D$58</f>
+        <f>F87-$D$69</f>
         <v/>
       </c>
       <c r="G90" s="18">
-        <f>G75-$D$58</f>
+        <f>G87-$D$69</f>
         <v/>
       </c>
       <c r="H90" s="18">
-        <f>H75-$D$58</f>
+        <f>H87-$D$69</f>
         <v/>
       </c>
       <c r="I90" s="18">
-        <f>I75-$D$58</f>
+        <f>I87-$D$69</f>
         <v/>
       </c>
       <c r="J90" s="18">
-        <f>J75-$D$58</f>
+        <f>J87-$D$69</f>
         <v/>
       </c>
       <c r="K90" s="18">
-        <f>K75-$D$58</f>
+        <f>K87-$D$69</f>
         <v/>
       </c>
       <c r="L90" s="18">
-        <f>L75-$D$58</f>
+        <f>L87-$D$69</f>
         <v/>
       </c>
       <c r="M90" s="18">
-        <f>M75-$D$58</f>
+        <f>M87-$D$69</f>
         <v/>
       </c>
       <c r="N90" s="18">
-        <f>N75-$D$58</f>
+        <f>N87-$D$69</f>
         <v/>
       </c>
     </row>
@@ -5327,43 +5314,43 @@
         </is>
       </c>
       <c r="E91" s="18">
-        <f>MAX(0,E78)*$D$50</f>
+        <f>MAX(0,E90)*$D$61</f>
         <v/>
       </c>
       <c r="F91" s="18">
-        <f>MAX(0,F78)*$D$50</f>
+        <f>MAX(0,F90)*$D$61</f>
         <v/>
       </c>
       <c r="G91" s="18">
-        <f>MAX(0,G78)*$D$50</f>
+        <f>MAX(0,G90)*$D$61</f>
         <v/>
       </c>
       <c r="H91" s="18">
-        <f>MAX(0,H78)*$D$50</f>
+        <f>MAX(0,H90)*$D$61</f>
         <v/>
       </c>
       <c r="I91" s="18">
-        <f>MAX(0,I78)*$D$50</f>
+        <f>MAX(0,I90)*$D$61</f>
         <v/>
       </c>
       <c r="J91" s="18">
-        <f>MAX(0,J78)*$D$50</f>
+        <f>MAX(0,J90)*$D$61</f>
         <v/>
       </c>
       <c r="K91" s="18">
-        <f>MAX(0,K78)*$D$50</f>
+        <f>MAX(0,K90)*$D$61</f>
         <v/>
       </c>
       <c r="L91" s="18">
-        <f>MAX(0,L78)*$D$50</f>
+        <f>MAX(0,L90)*$D$61</f>
         <v/>
       </c>
       <c r="M91" s="18">
-        <f>MAX(0,M78)*$D$50</f>
+        <f>MAX(0,M90)*$D$61</f>
         <v/>
       </c>
       <c r="N91" s="18">
-        <f>MAX(0,N78)*$D$50</f>
+        <f>MAX(0,N90)*$D$61</f>
         <v/>
       </c>
     </row>
@@ -5384,43 +5371,43 @@
         </is>
       </c>
       <c r="E92" s="21">
-        <f>IF(1=$D$38,$D$39,0)</f>
+        <f>IF(1=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="F92" s="21">
-        <f>IF(2=$D$38,$D$39,0)</f>
+        <f>IF(2=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="G92" s="21">
-        <f>IF(3=$D$38,$D$39,0)</f>
+        <f>IF(3=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="H92" s="21">
-        <f>IF(4=$D$38,$D$39,0)</f>
+        <f>IF(4=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="I92" s="21">
-        <f>IF(5=$D$38,$D$39,0)</f>
+        <f>IF(5=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="J92" s="21">
-        <f>IF(6=$D$38,$D$39,0)</f>
+        <f>IF(6=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="K92" s="21">
-        <f>IF(7=$D$38,$D$39,0)</f>
+        <f>IF(7=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="L92" s="21">
-        <f>IF(8=$D$38,$D$39,0)</f>
+        <f>IF(8=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="M92" s="21">
-        <f>IF(9=$D$38,$D$39,0)</f>
+        <f>IF(9=$D$49,$D$50,0)</f>
         <v/>
       </c>
       <c r="N92" s="21">
-        <f>IF(10=$D$38,$D$39,0)</f>
+        <f>IF(10=$D$49,$D$50,0)</f>
         <v/>
       </c>
     </row>
@@ -5441,47 +5428,46 @@
         </is>
       </c>
       <c r="E93" s="7">
-        <f>E75-E79-E80</f>
+        <f>E87-E91-E92</f>
         <v/>
       </c>
       <c r="F93" s="7">
-        <f>F75-F79-F80</f>
+        <f>F87-F91-F92</f>
         <v/>
       </c>
       <c r="G93" s="7">
-        <f>G75-G79-G80</f>
+        <f>G87-G91-G92</f>
         <v/>
       </c>
       <c r="H93" s="7">
-        <f>H75-H79-H80</f>
+        <f>H87-H91-H92</f>
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>I75-I79-I80</f>
+        <f>I87-I91-I92</f>
         <v/>
       </c>
       <c r="J93" s="7">
-        <f>J75-J79-J80</f>
+        <f>J87-J91-J92</f>
         <v/>
       </c>
       <c r="K93" s="7">
-        <f>K75-K79-K80</f>
+        <f>K87-K91-K92</f>
         <v/>
       </c>
       <c r="L93" s="7">
-        <f>L75-L79-L80</f>
+        <f>L87-L91-L92</f>
         <v/>
       </c>
       <c r="M93" s="7">
-        <f>M75-M79-M80</f>
+        <f>M87-M91-M92</f>
         <v/>
       </c>
       <c r="N93" s="7">
-        <f>N75-N79-N80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94"/>
+        <f>N87-N91-N92</f>
+        <v/>
+      </c>
+    </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -5518,44 +5504,47 @@
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
       <c r="E96" s="18">
-        <f>$D$57</f>
+        <f>$D$68</f>
         <v/>
       </c>
       <c r="F96" s="18">
-        <f>E91</f>
+        <f>E103</f>
         <v/>
       </c>
       <c r="G96" s="18">
-        <f>F91</f>
+        <f>F103</f>
         <v/>
       </c>
       <c r="H96" s="18">
-        <f>G91</f>
+        <f>G103</f>
         <v/>
       </c>
       <c r="I96" s="18">
-        <f>H91</f>
+        <f>H103</f>
         <v/>
       </c>
       <c r="J96" s="18">
-        <f>I91</f>
+        <f>I103</f>
         <v/>
       </c>
       <c r="K96" s="18">
-        <f>J91</f>
+        <f>J103</f>
         <v/>
       </c>
       <c r="L96" s="18">
-        <f>K91</f>
+        <f>K103</f>
         <v/>
       </c>
       <c r="M96" s="18">
-        <f>L91</f>
+        <f>L103</f>
         <v/>
       </c>
       <c r="N96" s="18">
-        <f>M91</f>
+        <f>M103</f>
         <v/>
       </c>
     </row>
@@ -5576,43 +5565,43 @@
         </is>
       </c>
       <c r="E97" s="18">
-        <f>E84*$D$43</f>
+        <f>E96*$D$54</f>
         <v/>
       </c>
       <c r="F97" s="18">
-        <f>F84*$D$43</f>
+        <f>F96*$D$54</f>
         <v/>
       </c>
       <c r="G97" s="18">
-        <f>G84*$D$43</f>
+        <f>G96*$D$54</f>
         <v/>
       </c>
       <c r="H97" s="18">
-        <f>H84*$D$43</f>
+        <f>H96*$D$54</f>
         <v/>
       </c>
       <c r="I97" s="18">
-        <f>I84*$D$43</f>
+        <f>I96*$D$54</f>
         <v/>
       </c>
       <c r="J97" s="18">
-        <f>J84*$D$43</f>
+        <f>J96*$D$54</f>
         <v/>
       </c>
       <c r="K97" s="18">
-        <f>K84*$D$43</f>
+        <f>K96*$D$54</f>
         <v/>
       </c>
       <c r="L97" s="18">
-        <f>L84*$D$43</f>
+        <f>L96*$D$54</f>
         <v/>
       </c>
       <c r="M97" s="18">
-        <f>M84*$D$43</f>
+        <f>M96*$D$54</f>
         <v/>
       </c>
       <c r="N97" s="18">
-        <f>N84*$D$43</f>
+        <f>N96*$D$54</f>
         <v/>
       </c>
     </row>
@@ -5633,43 +5622,43 @@
         </is>
       </c>
       <c r="E98" s="18">
-        <f>MIN($D$59,E84)</f>
+        <f>MIN($D$70,E96)</f>
         <v/>
       </c>
       <c r="F98" s="18">
-        <f>MIN($D$59,F84)</f>
+        <f>MIN($D$70,F96)</f>
         <v/>
       </c>
       <c r="G98" s="18">
-        <f>MIN($D$59,G84)</f>
+        <f>MIN($D$70,G96)</f>
         <v/>
       </c>
       <c r="H98" s="18">
-        <f>MIN($D$59,H84)</f>
+        <f>MIN($D$70,H96)</f>
         <v/>
       </c>
       <c r="I98" s="18">
-        <f>MIN($D$59,I84)</f>
+        <f>MIN($D$70,I96)</f>
         <v/>
       </c>
       <c r="J98" s="18">
-        <f>MIN($D$59,J84)</f>
+        <f>MIN($D$70,J96)</f>
         <v/>
       </c>
       <c r="K98" s="18">
-        <f>MIN($D$59,K84)</f>
+        <f>MIN($D$70,K96)</f>
         <v/>
       </c>
       <c r="L98" s="18">
-        <f>MIN($D$59,L84)</f>
+        <f>MIN($D$70,L96)</f>
         <v/>
       </c>
       <c r="M98" s="18">
-        <f>MIN($D$59,M84)</f>
+        <f>MIN($D$70,M96)</f>
         <v/>
       </c>
       <c r="N98" s="18">
-        <f>MIN($D$59,N84)</f>
+        <f>MIN($D$70,N96)</f>
         <v/>
       </c>
     </row>
@@ -5690,43 +5679,43 @@
         </is>
       </c>
       <c r="E99" s="18">
-        <f>E85+E86</f>
+        <f>E97+E98</f>
         <v/>
       </c>
       <c r="F99" s="18">
-        <f>F85+F86</f>
+        <f>F97+F98</f>
         <v/>
       </c>
       <c r="G99" s="18">
-        <f>G85+G86</f>
+        <f>G97+G98</f>
         <v/>
       </c>
       <c r="H99" s="18">
-        <f>H85+H86</f>
+        <f>H97+H98</f>
         <v/>
       </c>
       <c r="I99" s="18">
-        <f>I85+I86</f>
+        <f>I97+I98</f>
         <v/>
       </c>
       <c r="J99" s="18">
-        <f>J85+J86</f>
+        <f>J97+J98</f>
         <v/>
       </c>
       <c r="K99" s="18">
-        <f>K85+K86</f>
+        <f>K97+K98</f>
         <v/>
       </c>
       <c r="L99" s="18">
-        <f>L85+L86</f>
+        <f>L97+L98</f>
         <v/>
       </c>
       <c r="M99" s="18">
-        <f>M85+M86</f>
+        <f>M97+M98</f>
         <v/>
       </c>
       <c r="N99" s="18">
-        <f>N85+N86</f>
+        <f>N97+N98</f>
         <v/>
       </c>
     </row>
@@ -5747,43 +5736,43 @@
         </is>
       </c>
       <c r="E100" s="18">
-        <f>MAX(0,E81-E87-E97)</f>
+        <f>MAX(0,E93-E99-E109)</f>
         <v/>
       </c>
       <c r="F100" s="18">
-        <f>MAX(0,F81-F87-F97)</f>
+        <f>MAX(0,F93-F99-F109)</f>
         <v/>
       </c>
       <c r="G100" s="18">
-        <f>MAX(0,G81-G87-G97)</f>
+        <f>MAX(0,G93-G99-G109)</f>
         <v/>
       </c>
       <c r="H100" s="18">
-        <f>MAX(0,H81-H87-H97)</f>
+        <f>MAX(0,H93-H99-H109)</f>
         <v/>
       </c>
       <c r="I100" s="18">
-        <f>MAX(0,I81-I87-I97)</f>
+        <f>MAX(0,I93-I99-I109)</f>
         <v/>
       </c>
       <c r="J100" s="18">
-        <f>MAX(0,J81-J87-J97)</f>
+        <f>MAX(0,J93-J99-J109)</f>
         <v/>
       </c>
       <c r="K100" s="18">
-        <f>MAX(0,K81-K87-K97)</f>
+        <f>MAX(0,K93-K99-K109)</f>
         <v/>
       </c>
       <c r="L100" s="18">
-        <f>MAX(0,L81-L87-L97)</f>
+        <f>MAX(0,L93-L99-L109)</f>
         <v/>
       </c>
       <c r="M100" s="18">
-        <f>MAX(0,M81-M87-M97)</f>
+        <f>MAX(0,M93-M99-M109)</f>
         <v/>
       </c>
       <c r="N100" s="18">
-        <f>MAX(0,N81-N87-N97)</f>
+        <f>MAX(0,N93-N99-N109)</f>
         <v/>
       </c>
     </row>
@@ -5804,43 +5793,43 @@
         </is>
       </c>
       <c r="E101" s="21">
-        <f>MIN(MAX(0,E88)*$D$46,MAX(0,E84-E86))</f>
+        <f>MIN(E100*$D$57,MAX(0,E96-E98))</f>
         <v/>
       </c>
       <c r="F101" s="21">
-        <f>MIN(MAX(0,F88)*$D$46,MAX(0,F84-F86))</f>
+        <f>MIN(F100*$D$57,MAX(0,F96-F98))</f>
         <v/>
       </c>
       <c r="G101" s="21">
-        <f>MIN(MAX(0,G88)*$D$46,MAX(0,G84-G86))</f>
+        <f>MIN(G100*$D$57,MAX(0,G96-G98))</f>
         <v/>
       </c>
       <c r="H101" s="21">
-        <f>MIN(MAX(0,H88)*$D$46,MAX(0,H84-H86))</f>
+        <f>MIN(H100*$D$57,MAX(0,H96-H98))</f>
         <v/>
       </c>
       <c r="I101" s="21">
-        <f>MIN(MAX(0,I88)*$D$46,MAX(0,I84-I86))</f>
+        <f>MIN(I100*$D$57,MAX(0,I96-I98))</f>
         <v/>
       </c>
       <c r="J101" s="21">
-        <f>MIN(MAX(0,J88)*$D$46,MAX(0,J84-J86))</f>
+        <f>MIN(J100*$D$57,MAX(0,J96-J98))</f>
         <v/>
       </c>
       <c r="K101" s="21">
-        <f>MIN(MAX(0,K88)*$D$46,MAX(0,K84-K86))</f>
+        <f>MIN(K100*$D$57,MAX(0,K96-K98))</f>
         <v/>
       </c>
       <c r="L101" s="21">
-        <f>MIN(MAX(0,L88)*$D$46,MAX(0,L84-L86))</f>
+        <f>MIN(L100*$D$57,MAX(0,L96-L98))</f>
         <v/>
       </c>
       <c r="M101" s="21">
-        <f>MIN(MAX(0,M88)*$D$46,MAX(0,M84-M86))</f>
+        <f>MIN(M100*$D$57,MAX(0,M96-M98))</f>
         <v/>
       </c>
       <c r="N101" s="21">
-        <f>MIN(MAX(0,N88)*$D$46,MAX(0,N84-N86))</f>
+        <f>MIN(N100*$D$57,MAX(0,N96-N98))</f>
         <v/>
       </c>
     </row>
@@ -5861,43 +5850,43 @@
         </is>
       </c>
       <c r="E102" s="18">
-        <f>E86+E89</f>
+        <f>E98+E101</f>
         <v/>
       </c>
       <c r="F102" s="18">
-        <f>F86+F89</f>
+        <f>F98+F101</f>
         <v/>
       </c>
       <c r="G102" s="18">
-        <f>G86+G89</f>
+        <f>G98+G101</f>
         <v/>
       </c>
       <c r="H102" s="18">
-        <f>H86+H89</f>
+        <f>H98+H101</f>
         <v/>
       </c>
       <c r="I102" s="18">
-        <f>I86+I89</f>
+        <f>I98+I101</f>
         <v/>
       </c>
       <c r="J102" s="18">
-        <f>J86+J89</f>
+        <f>J98+J101</f>
         <v/>
       </c>
       <c r="K102" s="18">
-        <f>K86+K89</f>
+        <f>K98+K101</f>
         <v/>
       </c>
       <c r="L102" s="18">
-        <f>L86+L89</f>
+        <f>L98+L101</f>
         <v/>
       </c>
       <c r="M102" s="18">
-        <f>M86+M89</f>
+        <f>M98+M101</f>
         <v/>
       </c>
       <c r="N102" s="18">
-        <f>N86+N89</f>
+        <f>N98+N101</f>
         <v/>
       </c>
     </row>
@@ -5917,44 +5906,48 @@
           <t>MAX(0, Beg - Total Prin)</t>
         </is>
       </c>
+      <c r="D103">
+        <f>$D$68</f>
+        <v/>
+      </c>
       <c r="E103" s="18">
-        <f>MAX(0,E84-E90)</f>
+        <f>MAX(0,E96-E102)</f>
         <v/>
       </c>
       <c r="F103" s="18">
-        <f>MAX(0,F84-F90)</f>
+        <f>MAX(0,F96-F102)</f>
         <v/>
       </c>
       <c r="G103" s="18">
-        <f>MAX(0,G84-G90)</f>
+        <f>MAX(0,G96-G102)</f>
         <v/>
       </c>
       <c r="H103" s="18">
-        <f>MAX(0,H84-H90)</f>
+        <f>MAX(0,H96-H102)</f>
         <v/>
       </c>
       <c r="I103" s="18">
-        <f>MAX(0,I84-I90)</f>
+        <f>MAX(0,I96-I102)</f>
         <v/>
       </c>
       <c r="J103" s="18">
-        <f>MAX(0,J84-J90)</f>
+        <f>MAX(0,J96-J102)</f>
         <v/>
       </c>
       <c r="K103" s="18">
-        <f>MAX(0,K84-K90)</f>
+        <f>MAX(0,K96-K102)</f>
         <v/>
       </c>
       <c r="L103" s="18">
-        <f>MAX(0,L84-L90)</f>
+        <f>MAX(0,L96-L102)</f>
         <v/>
       </c>
       <c r="M103" s="18">
-        <f>MAX(0,M84-M90)</f>
+        <f>MAX(0,M96-M102)</f>
         <v/>
       </c>
       <c r="N103" s="18">
-        <f>MAX(0,N84-N90)</f>
+        <f>MAX(0,N96-N102)</f>
         <v/>
       </c>
     </row>
@@ -5975,43 +5968,43 @@
         </is>
       </c>
       <c r="E104" s="24">
-        <f>IF(E87&gt;0,E81/E87,0)</f>
+        <f>IF(E99&gt;0,E93/E99,0)</f>
         <v/>
       </c>
       <c r="F104" s="24">
-        <f>IF(F87&gt;0,F81/F87,0)</f>
+        <f>IF(F99&gt;0,F93/F99,0)</f>
         <v/>
       </c>
       <c r="G104" s="24">
-        <f>IF(G87&gt;0,G81/G87,0)</f>
+        <f>IF(G99&gt;0,G93/G99,0)</f>
         <v/>
       </c>
       <c r="H104" s="24">
-        <f>IF(H87&gt;0,H81/H87,0)</f>
+        <f>IF(H99&gt;0,H93/H99,0)</f>
         <v/>
       </c>
       <c r="I104" s="24">
-        <f>IF(I87&gt;0,I81/I87,0)</f>
+        <f>IF(I99&gt;0,I93/I99,0)</f>
         <v/>
       </c>
       <c r="J104" s="24">
-        <f>IF(J87&gt;0,J81/J87,0)</f>
+        <f>IF(J99&gt;0,J93/J99,0)</f>
         <v/>
       </c>
       <c r="K104" s="24">
-        <f>IF(K87&gt;0,K81/K87,0)</f>
+        <f>IF(K99&gt;0,K93/K99,0)</f>
         <v/>
       </c>
       <c r="L104" s="24">
-        <f>IF(L87&gt;0,L81/L87,0)</f>
+        <f>IF(L99&gt;0,L93/L99,0)</f>
         <v/>
       </c>
       <c r="M104" s="24">
-        <f>IF(M87&gt;0,M81/M87,0)</f>
+        <f>IF(M99&gt;0,M93/M99,0)</f>
         <v/>
       </c>
       <c r="N104" s="24">
-        <f>IF(N87&gt;0,N81/N87,0)</f>
+        <f>IF(N99&gt;0,N93/N99,0)</f>
         <v/>
       </c>
     </row>
@@ -6032,43 +6025,43 @@
         </is>
       </c>
       <c r="E105" s="18">
-        <f>MAX(0,$D$57-(1-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(1-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="F105" s="18">
-        <f>MAX(0,$D$57-(2-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(2-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="G105" s="18">
-        <f>MAX(0,$D$57-(3-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(3-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="H105" s="18">
-        <f>MAX(0,$D$57-(4-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(4-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="I105" s="18">
-        <f>MAX(0,$D$57-(5-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(5-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="J105" s="18">
-        <f>MAX(0,$D$57-(6-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(6-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="K105" s="18">
-        <f>MAX(0,$D$57-(7-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(7-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="L105" s="18">
-        <f>MAX(0,$D$57-(8-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(8-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="M105" s="18">
-        <f>MAX(0,$D$57-(9-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(9-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
       <c r="N105" s="18">
-        <f>MAX(0,$D$57-(10-1)*$D$59)*$D$43+$D$59</f>
+        <f>MAX(0,$D$68-(10-1)*$D$70)*$D$54+$D$70</f>
         <v/>
       </c>
     </row>
@@ -6113,44 +6106,43 @@
         <v/>
       </c>
       <c r="E107" s="18">
-        <f>F93*$D$45/12</f>
+        <f>F105*$D$56/12</f>
         <v/>
       </c>
       <c r="F107" s="18">
-        <f>G93*$D$45/12</f>
+        <f>G105*$D$56/12</f>
         <v/>
       </c>
       <c r="G107" s="18">
-        <f>H93*$D$45/12</f>
+        <f>H105*$D$56/12</f>
         <v/>
       </c>
       <c r="H107" s="18">
-        <f>I93*$D$45/12</f>
+        <f>I105*$D$56/12</f>
         <v/>
       </c>
       <c r="I107" s="18">
-        <f>J93*$D$45/12</f>
+        <f>J105*$D$56/12</f>
         <v/>
       </c>
       <c r="J107" s="18">
-        <f>K93*$D$45/12</f>
+        <f>K105*$D$56/12</f>
         <v/>
       </c>
       <c r="K107" s="18">
-        <f>L93*$D$45/12</f>
+        <f>L105*$D$56/12</f>
         <v/>
       </c>
       <c r="L107" s="18">
-        <f>M93*$D$45/12</f>
+        <f>M105*$D$56/12</f>
         <v/>
       </c>
       <c r="M107" s="18">
-        <f>N93*$D$45/12</f>
-        <v/>
-      </c>
-      <c r="N107" s="18">
-        <f>0</f>
-        <v/>
+        <f>N105*$D$56/12</f>
+        <v/>
+      </c>
+      <c r="N107" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -6165,48 +6157,47 @@
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr"/>
-      <c r="D108" s="18">
-        <f>0</f>
-        <v/>
+      <c r="D108" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="18">
-        <f>D98</f>
+        <f>D121</f>
         <v/>
       </c>
       <c r="F108" s="18">
-        <f>E98</f>
+        <f>E110</f>
         <v/>
       </c>
       <c r="G108" s="18">
-        <f>F98</f>
+        <f>F110</f>
         <v/>
       </c>
       <c r="H108" s="18">
-        <f>G98</f>
+        <f>G110</f>
         <v/>
       </c>
       <c r="I108" s="18">
-        <f>H98</f>
+        <f>H110</f>
         <v/>
       </c>
       <c r="J108" s="18">
-        <f>I98</f>
+        <f>I110</f>
         <v/>
       </c>
       <c r="K108" s="18">
-        <f>J98</f>
+        <f>J110</f>
         <v/>
       </c>
       <c r="L108" s="18">
-        <f>K98</f>
+        <f>K110</f>
         <v/>
       </c>
       <c r="M108" s="18">
-        <f>L98</f>
+        <f>L110</f>
         <v/>
       </c>
       <c r="N108" s="18">
-        <f>M98</f>
+        <f>M110</f>
         <v/>
       </c>
     </row>
@@ -6231,43 +6222,43 @@
         <v/>
       </c>
       <c r="E109" s="18">
-        <f>E95-E96</f>
+        <f>E107-E108</f>
         <v/>
       </c>
       <c r="F109" s="18">
-        <f>F95-F96</f>
+        <f>F107-F108</f>
         <v/>
       </c>
       <c r="G109" s="18">
-        <f>G95-G96</f>
+        <f>G107-G108</f>
         <v/>
       </c>
       <c r="H109" s="18">
-        <f>H95-H96</f>
+        <f>H107-H108</f>
         <v/>
       </c>
       <c r="I109" s="18">
-        <f>I95-I96</f>
+        <f>I107-I108</f>
         <v/>
       </c>
       <c r="J109" s="18">
-        <f>J95-J96</f>
+        <f>J107-J108</f>
         <v/>
       </c>
       <c r="K109" s="18">
-        <f>K95-K96</f>
+        <f>K107-K108</f>
         <v/>
       </c>
       <c r="L109" s="18">
-        <f>L95-L96</f>
+        <f>L107-L108</f>
         <v/>
       </c>
       <c r="M109" s="18">
-        <f>M95-M96</f>
+        <f>M107-M108</f>
         <v/>
       </c>
       <c r="N109" s="18">
-        <f>N95-N96</f>
+        <f>N107-N108</f>
         <v/>
       </c>
     </row>
@@ -6292,47 +6283,46 @@
         <v/>
       </c>
       <c r="E110" s="18">
-        <f>E96+E97</f>
+        <f>E108+E109</f>
         <v/>
       </c>
       <c r="F110" s="18">
-        <f>F96+F97</f>
+        <f>F108+F109</f>
         <v/>
       </c>
       <c r="G110" s="18">
-        <f>G96+G97</f>
+        <f>G108+G109</f>
         <v/>
       </c>
       <c r="H110" s="18">
-        <f>H96+H97</f>
+        <f>H108+H109</f>
         <v/>
       </c>
       <c r="I110" s="18">
-        <f>I96+I97</f>
+        <f>I108+I109</f>
         <v/>
       </c>
       <c r="J110" s="18">
-        <f>J96+J97</f>
+        <f>J108+J109</f>
         <v/>
       </c>
       <c r="K110" s="18">
-        <f>K96+K97</f>
+        <f>K108+K109</f>
         <v/>
       </c>
       <c r="L110" s="18">
-        <f>L96+L97</f>
+        <f>L108+L109</f>
         <v/>
       </c>
       <c r="M110" s="18">
-        <f>M96+M97</f>
+        <f>M108+M109</f>
         <v/>
       </c>
       <c r="N110" s="18">
-        <f>N96+N97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111"/>
+        <f>N108+N109</f>
+        <v/>
+      </c>
+    </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
@@ -6370,43 +6360,43 @@
         </is>
       </c>
       <c r="E113" s="18">
-        <f>E81-(E85+E90)-E97</f>
+        <f>E93-E97-E102-E109</f>
         <v/>
       </c>
       <c r="F113" s="18">
-        <f>F81-(F85+F90)-F97</f>
+        <f>F93-F97-F102-F109</f>
         <v/>
       </c>
       <c r="G113" s="18">
-        <f>G81-(G85+G90)-G97</f>
+        <f>G93-G97-G102-G109</f>
         <v/>
       </c>
       <c r="H113" s="18">
-        <f>H81-(H85+H90)-H97</f>
+        <f>H93-H97-H102-H109</f>
         <v/>
       </c>
       <c r="I113" s="18">
-        <f>I81-(I85+I90)-I97</f>
+        <f>I93-I97-I102-I109</f>
         <v/>
       </c>
       <c r="J113" s="18">
-        <f>J81-(J85+J90)-J97</f>
+        <f>J93-J97-J102-J109</f>
         <v/>
       </c>
       <c r="K113" s="18">
-        <f>K81-(K85+K90)-K97</f>
+        <f>K93-K97-K102-K109</f>
         <v/>
       </c>
       <c r="L113" s="18">
-        <f>L81-(L85+L90)-L97</f>
+        <f>L93-L97-L102-L109</f>
         <v/>
       </c>
       <c r="M113" s="18">
-        <f>M81-(M85+M90)-M97</f>
+        <f>M93-M97-M102-M109</f>
         <v/>
       </c>
       <c r="N113" s="18">
-        <f>N81-(N85+N90)-N97</f>
+        <f>N93-N97-N102-N109</f>
         <v/>
       </c>
     </row>
@@ -6423,43 +6413,43 @@
         </is>
       </c>
       <c r="E114" s="22">
-        <f>IF(E92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(E104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="F114" s="22">
-        <f>IF(F92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(F104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="G114" s="22">
-        <f>IF(G92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(G104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="H114" s="22">
-        <f>IF(H92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(H104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="I114" s="22">
-        <f>IF(I92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(I104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="J114" s="22">
-        <f>IF(J92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(J104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="K114" s="22">
-        <f>IF(K92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(K104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="L114" s="22">
-        <f>IF(L92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(L104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="M114" s="22">
-        <f>IF(M92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(M104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="N114" s="22">
-        <f>IF(N92&gt;=$D$47,"PASS","LOCKED")</f>
+        <f>IF(N104&gt;=$D$58,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
@@ -6480,47 +6470,46 @@
         </is>
       </c>
       <c r="E115" s="7">
-        <f>IF(E102="PASS",MAX(0,E101),0)</f>
+        <f>IF(E114="PASS",MAX(0,E113),0)</f>
         <v/>
       </c>
       <c r="F115" s="7">
-        <f>IF(F102="PASS",MAX(0,F101),0)</f>
+        <f>IF(F114="PASS",MAX(0,F113),0)</f>
         <v/>
       </c>
       <c r="G115" s="7">
-        <f>IF(G102="PASS",MAX(0,G101),0)</f>
+        <f>IF(G114="PASS",MAX(0,G113),0)</f>
         <v/>
       </c>
       <c r="H115" s="7">
-        <f>IF(H102="PASS",MAX(0,H101),0)</f>
+        <f>IF(H114="PASS",MAX(0,H113),0)</f>
         <v/>
       </c>
       <c r="I115" s="7">
-        <f>IF(I102="PASS",MAX(0,I101),0)</f>
+        <f>IF(I114="PASS",MAX(0,I113),0)</f>
         <v/>
       </c>
       <c r="J115" s="7">
-        <f>IF(J102="PASS",MAX(0,J101),0)</f>
+        <f>IF(J114="PASS",MAX(0,J113),0)</f>
         <v/>
       </c>
       <c r="K115" s="7">
-        <f>IF(K102="PASS",MAX(0,K101),0)</f>
+        <f>IF(K114="PASS",MAX(0,K113),0)</f>
         <v/>
       </c>
       <c r="L115" s="7">
-        <f>IF(L102="PASS",MAX(0,L101),0)</f>
+        <f>IF(L114="PASS",MAX(0,L113),0)</f>
         <v/>
       </c>
       <c r="M115" s="7">
-        <f>IF(M102="PASS",MAX(0,M101),0)</f>
+        <f>IF(M114="PASS",MAX(0,M113),0)</f>
         <v/>
       </c>
       <c r="N115" s="7">
-        <f>IF(N102="PASS",MAX(0,N101),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116"/>
+        <f>IF(N114="PASS",MAX(0,N113),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
@@ -6563,7 +6552,7 @@
       </c>
       <c r="C119" s="6" t="inlineStr"/>
       <c r="D119" s="18">
-        <f>$D$17</f>
+        <f>$D$28</f>
         <v/>
       </c>
     </row>
@@ -6580,7 +6569,7 @@
       </c>
       <c r="C120" s="6" t="inlineStr"/>
       <c r="D120" s="18">
-        <f>$D$17*$D$18</f>
+        <f>$D$28*$D$29</f>
         <v/>
       </c>
     </row>
@@ -6597,7 +6586,7 @@
       </c>
       <c r="C121" s="6" t="inlineStr"/>
       <c r="D121" s="18">
-        <f>D95</f>
+        <f>E107</f>
         <v/>
       </c>
     </row>
@@ -6614,11 +6603,10 @@
       </c>
       <c r="C122" s="6" t="inlineStr"/>
       <c r="D122" s="7">
-        <f>D107+D108+D109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123"/>
+        <f>D119+D120+D121</f>
+        <v/>
+      </c>
+    </row>
     <row r="124">
       <c r="A124" s="23" t="inlineStr">
         <is>
@@ -6641,7 +6629,7 @@
       </c>
       <c r="C125" s="6" t="inlineStr"/>
       <c r="D125" s="18">
-        <f>$D$57</f>
+        <f>$D$28*$D$53</f>
         <v/>
       </c>
     </row>
@@ -6662,7 +6650,7 @@
         </is>
       </c>
       <c r="D126" s="18">
-        <f>D110-D113</f>
+        <f>D122-D125</f>
         <v/>
       </c>
     </row>
@@ -6679,7 +6667,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr"/>
       <c r="D127" s="7">
-        <f>D113+D114</f>
+        <f>D125+D126</f>
         <v/>
       </c>
     </row>
@@ -6692,11 +6680,10 @@
       <c r="B128" s="6" t="inlineStr"/>
       <c r="C128" s="6" t="inlineStr"/>
       <c r="D128" s="10">
-        <f>IF(ABS(D110-D115)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129"/>
+        <f>IF(ABS(D122-D127)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
@@ -6733,6 +6720,10 @@
           <t>Exit Multiple × Exit Yr EBITDA</t>
         </is>
       </c>
+      <c r="D131">
+        <f>K87*$D$30</f>
+        <v/>
+      </c>
       <c r="K131" s="18">
         <f>$D$19*K75</f>
         <v/>
@@ -6754,6 +6745,10 @@
           <t>Ending Bal at Exit</t>
         </is>
       </c>
+      <c r="D132">
+        <f>K103</f>
+        <v/>
+      </c>
       <c r="K132" s="18">
         <f>K91</f>
         <v/>
@@ -6775,6 +6770,10 @@
           <t>DSRA Ending at Exit</t>
         </is>
       </c>
+      <c r="D133">
+        <f>K110</f>
+        <v/>
+      </c>
       <c r="K133" s="18">
         <f>K98</f>
         <v/>
@@ -6796,12 +6795,15 @@
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
+      <c r="D134">
+        <f>D131-D132+D133</f>
+        <v/>
+      </c>
       <c r="K134" s="7">
         <f>K119-K120+K121</f>
         <v/>
       </c>
     </row>
-    <row r="135"/>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
@@ -6835,48 +6837,45 @@
       </c>
       <c r="C137" s="6" t="inlineStr"/>
       <c r="D137" s="18">
-        <f>-D114</f>
+        <f>-D126</f>
         <v/>
       </c>
       <c r="E137" s="18">
-        <f>E103</f>
+        <f>E115</f>
         <v/>
       </c>
       <c r="F137" s="18">
-        <f>F103</f>
+        <f>F115</f>
         <v/>
       </c>
       <c r="G137" s="18">
-        <f>G103</f>
+        <f>G115</f>
         <v/>
       </c>
       <c r="H137" s="18">
-        <f>H103</f>
+        <f>H115</f>
         <v/>
       </c>
       <c r="I137" s="18">
-        <f>I103</f>
+        <f>I115</f>
         <v/>
       </c>
       <c r="J137" s="18">
-        <f>J103</f>
+        <f>J115</f>
         <v/>
       </c>
       <c r="K137" s="18">
-        <f>K103+K122</f>
-        <v/>
-      </c>
-      <c r="L137" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M137" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N137" s="18">
-        <f>0</f>
-        <v/>
+        <f>K115+D134</f>
+        <v/>
+      </c>
+      <c r="L137" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6896,7 +6895,7 @@
         </is>
       </c>
       <c r="D138" s="25">
-        <f>IRR(D125:K125)</f>
+        <f>IRR(D137:N137)</f>
         <v/>
       </c>
     </row>
@@ -6917,11 +6916,10 @@
         </is>
       </c>
       <c r="D139" s="24">
-        <f>SUMIF(D125:K125,"&gt;0")/ABS(D125)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140"/>
+        <f>(SUM(E137:K137))/-D137</f>
+        <v/>
+      </c>
+    </row>
     <row r="141">
       <c r="A141" s="23" t="inlineStr">
         <is>
@@ -6944,48 +6942,45 @@
       </c>
       <c r="C142" s="6" t="inlineStr"/>
       <c r="D142" s="18">
-        <f>-$D$17-D108</f>
+        <f>-$D$28-D120</f>
         <v/>
       </c>
       <c r="E142" s="18">
-        <f>E81</f>
+        <f>E93</f>
         <v/>
       </c>
       <c r="F142" s="18">
-        <f>F81</f>
+        <f>F93</f>
         <v/>
       </c>
       <c r="G142" s="18">
-        <f>G81</f>
+        <f>G93</f>
         <v/>
       </c>
       <c r="H142" s="18">
-        <f>H81</f>
+        <f>H93</f>
         <v/>
       </c>
       <c r="I142" s="18">
-        <f>I81</f>
+        <f>I93</f>
         <v/>
       </c>
       <c r="J142" s="18">
-        <f>J81</f>
+        <f>J93</f>
         <v/>
       </c>
       <c r="K142" s="18">
-        <f>K81+K119</f>
-        <v/>
-      </c>
-      <c r="L142" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M142" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N142" s="18">
-        <f>0</f>
-        <v/>
+        <f>K93+D131</f>
+        <v/>
+      </c>
+      <c r="L142" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -7005,7 +7000,7 @@
         </is>
       </c>
       <c r="D143" s="25">
-        <f>IRR(D130:K130)</f>
+        <f>IRR(D142:N142)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -3735,7 +3735,7 @@
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="10">
-        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <f>IF(K103&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -3721,10 +3721,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="10">
-        <f>D116</f>
-        <v/>
-      </c>
+      <c r="D22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -3752,7 +3749,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(MINIFS(E104:K104,E104:K104,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_2_Peaker.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -240,6 +240,7 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3503,10 +3504,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="n"/>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="56">
+        <f>IF(COUNTIF(E104:K104,"&gt;0")&gt;0,MINIFS(E104:K104,E104:K104,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="47" t="inlineStr">
@@ -3749,7 +3765,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>IF(MINIFS(E104:K104,E104:K104,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
